--- a/api/tests/testthat/fixtures/surveymonkey/golden/Docentes_inst.xlsx
+++ b/api/tests/testthat/fixtures/surveymonkey/golden/Docentes_inst.xlsx
@@ -881,7 +881,7 @@
     <t xml:space="preserve">es</t>
   </si>
   <si>
-    <t xml:space="preserve">20260430</t>
+    <t xml:space="preserve">20260502</t>
   </si>
   <si>
     <t xml:space="preserve">order</t>

--- a/api/tests/testthat/fixtures/surveymonkey/golden/Docentes_inst.xlsx
+++ b/api/tests/testthat/fixtures/surveymonkey/golden/Docentes_inst.xlsx
@@ -881,7 +881,7 @@
     <t xml:space="preserve">es</t>
   </si>
   <si>
-    <t xml:space="preserve">20260502</t>
+    <t xml:space="preserve">20260523</t>
   </si>
   <si>
     <t xml:space="preserve">order</t>
@@ -1594,11 +1594,21 @@
       <c r="C2" t="s">
         <v>11</v>
       </c>
-      <c r="D2"/>
-      <c r="E2"/>
-      <c r="F2"/>
-      <c r="G2"/>
-      <c r="H2"/>
+      <c r="D2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H2" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I2" t="s">
         <v>10</v>
       </c>
@@ -1613,11 +1623,21 @@
       <c r="C3" t="s">
         <v>13</v>
       </c>
-      <c r="D3"/>
-      <c r="E3"/>
-      <c r="F3"/>
-      <c r="G3"/>
-      <c r="H3"/>
+      <c r="D3" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E3" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F3" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G3" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H3" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I3" t="s">
         <v>10</v>
       </c>
@@ -1626,13 +1646,27 @@
       <c r="A4" t="s">
         <v>14</v>
       </c>
-      <c r="B4"/>
-      <c r="C4"/>
-      <c r="D4"/>
-      <c r="E4"/>
-      <c r="F4"/>
-      <c r="G4"/>
-      <c r="H4"/>
+      <c r="B4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H4" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I4" t="s">
         <v>10</v>
       </c>
@@ -1647,11 +1681,21 @@
       <c r="C5" t="s">
         <v>17</v>
       </c>
-      <c r="D5"/>
-      <c r="E5"/>
-      <c r="F5"/>
-      <c r="G5"/>
-      <c r="H5"/>
+      <c r="D5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H5" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I5" t="s">
         <v>18</v>
       </c>
@@ -1666,11 +1710,21 @@
       <c r="C6" t="s">
         <v>20</v>
       </c>
-      <c r="D6"/>
-      <c r="E6"/>
-      <c r="F6"/>
-      <c r="G6"/>
-      <c r="H6"/>
+      <c r="D6" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E6" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F6" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G6" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H6" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I6" t="s">
         <v>19</v>
       </c>
@@ -1685,11 +1739,21 @@
       <c r="C7" t="s">
         <v>23</v>
       </c>
-      <c r="D7"/>
-      <c r="E7"/>
-      <c r="F7"/>
-      <c r="G7"/>
-      <c r="H7"/>
+      <c r="D7" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E7" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F7" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G7" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H7" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I7" t="s">
         <v>19</v>
       </c>
@@ -1698,13 +1762,27 @@
       <c r="A8" t="s">
         <v>14</v>
       </c>
-      <c r="B8"/>
-      <c r="C8"/>
-      <c r="D8"/>
-      <c r="E8"/>
-      <c r="F8"/>
-      <c r="G8"/>
-      <c r="H8"/>
+      <c r="B8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H8" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I8" t="s">
         <v>19</v>
       </c>
@@ -1719,11 +1797,21 @@
       <c r="C9" t="s">
         <v>26</v>
       </c>
-      <c r="D9"/>
-      <c r="E9"/>
-      <c r="F9"/>
-      <c r="G9"/>
-      <c r="H9"/>
+      <c r="D9" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E9" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F9" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G9" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H9" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I9" t="s">
         <v>18</v>
       </c>
@@ -1738,11 +1826,21 @@
       <c r="C10" t="s">
         <v>29</v>
       </c>
-      <c r="D10"/>
-      <c r="E10"/>
-      <c r="F10"/>
-      <c r="G10"/>
-      <c r="H10"/>
+      <c r="D10" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E10" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F10" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G10" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H10" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I10" t="s">
         <v>18</v>
       </c>
@@ -1757,11 +1855,21 @@
       <c r="C11" t="s">
         <v>31</v>
       </c>
-      <c r="D11"/>
-      <c r="E11"/>
-      <c r="F11"/>
-      <c r="G11"/>
-      <c r="H11"/>
+      <c r="D11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H11" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I11" t="s">
         <v>18</v>
       </c>
@@ -1776,11 +1884,21 @@
       <c r="C12" t="s">
         <v>33</v>
       </c>
-      <c r="D12"/>
-      <c r="E12"/>
-      <c r="F12"/>
-      <c r="G12"/>
-      <c r="H12"/>
+      <c r="D12" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E12" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F12" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G12" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H12" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I12" t="s">
         <v>18</v>
       </c>
@@ -1795,11 +1913,21 @@
       <c r="C13" t="s">
         <v>35</v>
       </c>
-      <c r="D13"/>
-      <c r="E13"/>
-      <c r="F13"/>
-      <c r="G13"/>
-      <c r="H13"/>
+      <c r="D13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H13" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I13" t="s">
         <v>36</v>
       </c>
@@ -1814,11 +1942,21 @@
       <c r="C14" t="s">
         <v>35</v>
       </c>
-      <c r="D14"/>
-      <c r="E14"/>
-      <c r="F14"/>
-      <c r="G14"/>
-      <c r="H14"/>
+      <c r="D14" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E14" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F14" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G14" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H14" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I14" t="s">
         <v>36</v>
       </c>
@@ -1833,11 +1971,21 @@
       <c r="C15" t="s">
         <v>39</v>
       </c>
-      <c r="D15"/>
-      <c r="E15"/>
-      <c r="F15"/>
-      <c r="G15"/>
-      <c r="H15"/>
+      <c r="D15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H15" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I15" t="s">
         <v>36</v>
       </c>
@@ -1852,11 +2000,21 @@
       <c r="C16" t="s">
         <v>41</v>
       </c>
-      <c r="D16"/>
-      <c r="E16"/>
-      <c r="F16"/>
-      <c r="G16"/>
-      <c r="H16"/>
+      <c r="D16" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E16" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F16" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G16" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H16" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I16" t="s">
         <v>36</v>
       </c>
@@ -1865,13 +2023,27 @@
       <c r="A17" t="s">
         <v>14</v>
       </c>
-      <c r="B17"/>
-      <c r="C17"/>
-      <c r="D17"/>
-      <c r="E17"/>
-      <c r="F17"/>
-      <c r="G17"/>
-      <c r="H17"/>
+      <c r="B17" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C17" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D17" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E17" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F17" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G17" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H17" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I17" t="s">
         <v>36</v>
       </c>
@@ -1886,11 +2058,21 @@
       <c r="C18" t="s">
         <v>44</v>
       </c>
-      <c r="D18"/>
-      <c r="E18"/>
-      <c r="F18"/>
-      <c r="G18"/>
-      <c r="H18"/>
+      <c r="D18" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E18" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F18" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G18" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H18" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I18" t="s">
         <v>18</v>
       </c>
@@ -1902,12 +2084,24 @@
       <c r="B19" t="s">
         <v>45</v>
       </c>
-      <c r="C19"/>
-      <c r="D19"/>
-      <c r="E19"/>
-      <c r="F19"/>
-      <c r="G19"/>
-      <c r="H19"/>
+      <c r="C19" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D19" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E19" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F19" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G19" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H19" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I19" t="s">
         <v>46</v>
       </c>
@@ -1922,11 +2116,21 @@
       <c r="C20" t="s">
         <v>49</v>
       </c>
-      <c r="D20"/>
-      <c r="E20"/>
-      <c r="F20"/>
-      <c r="G20"/>
-      <c r="H20"/>
+      <c r="D20" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E20" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F20" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G20" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H20" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I20" t="s">
         <v>46</v>
       </c>
@@ -1941,11 +2145,21 @@
       <c r="C21" t="s">
         <v>51</v>
       </c>
-      <c r="D21"/>
-      <c r="E21"/>
-      <c r="F21"/>
-      <c r="G21"/>
-      <c r="H21"/>
+      <c r="D21" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E21" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F21" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G21" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H21" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I21" t="s">
         <v>46</v>
       </c>
@@ -1960,11 +2174,21 @@
       <c r="C22" t="s">
         <v>53</v>
       </c>
-      <c r="D22"/>
-      <c r="E22"/>
-      <c r="F22"/>
-      <c r="G22"/>
-      <c r="H22"/>
+      <c r="D22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H22" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I22" t="s">
         <v>46</v>
       </c>
@@ -1973,13 +2197,27 @@
       <c r="A23" t="s">
         <v>14</v>
       </c>
-      <c r="B23"/>
-      <c r="C23"/>
-      <c r="D23"/>
-      <c r="E23"/>
-      <c r="F23"/>
-      <c r="G23"/>
-      <c r="H23"/>
+      <c r="B23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H23" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I23" t="s">
         <v>46</v>
       </c>
@@ -1991,12 +2229,24 @@
       <c r="B24" t="s">
         <v>54</v>
       </c>
-      <c r="C24"/>
-      <c r="D24"/>
-      <c r="E24"/>
-      <c r="F24"/>
-      <c r="G24"/>
-      <c r="H24"/>
+      <c r="C24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H24" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I24" t="s">
         <v>55</v>
       </c>
@@ -2011,11 +2261,21 @@
       <c r="C25" t="s">
         <v>57</v>
       </c>
-      <c r="D25"/>
-      <c r="E25"/>
-      <c r="F25"/>
-      <c r="G25"/>
-      <c r="H25"/>
+      <c r="D25" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E25" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F25" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G25" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H25" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I25" t="s">
         <v>55</v>
       </c>
@@ -2030,11 +2290,21 @@
       <c r="C26" t="s">
         <v>59</v>
       </c>
-      <c r="D26"/>
-      <c r="E26"/>
-      <c r="F26"/>
-      <c r="G26"/>
-      <c r="H26"/>
+      <c r="D26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H26" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I26" t="s">
         <v>55</v>
       </c>
@@ -2049,11 +2319,21 @@
       <c r="C27" t="s">
         <v>61</v>
       </c>
-      <c r="D27"/>
-      <c r="E27"/>
-      <c r="F27"/>
-      <c r="G27"/>
-      <c r="H27"/>
+      <c r="D27" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E27" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F27" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G27" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H27" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I27" t="s">
         <v>55</v>
       </c>
@@ -2068,11 +2348,21 @@
       <c r="C28" t="s">
         <v>63</v>
       </c>
-      <c r="D28"/>
-      <c r="E28"/>
-      <c r="F28"/>
-      <c r="G28"/>
-      <c r="H28"/>
+      <c r="D28" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E28" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F28" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G28" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H28" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I28" t="s">
         <v>55</v>
       </c>
@@ -2087,11 +2377,21 @@
       <c r="C29" t="s">
         <v>65</v>
       </c>
-      <c r="D29"/>
-      <c r="E29"/>
-      <c r="F29"/>
-      <c r="G29"/>
-      <c r="H29"/>
+      <c r="D29" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E29" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F29" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G29" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H29" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I29" t="s">
         <v>55</v>
       </c>
@@ -2106,11 +2406,21 @@
       <c r="C30" t="s">
         <v>67</v>
       </c>
-      <c r="D30"/>
-      <c r="E30"/>
-      <c r="F30"/>
-      <c r="G30"/>
-      <c r="H30"/>
+      <c r="D30" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E30" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F30" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G30" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H30" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I30" t="s">
         <v>55</v>
       </c>
@@ -2125,11 +2435,21 @@
       <c r="C31" t="s">
         <v>69</v>
       </c>
-      <c r="D31"/>
-      <c r="E31"/>
-      <c r="F31"/>
-      <c r="G31"/>
-      <c r="H31"/>
+      <c r="D31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H31" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I31" t="s">
         <v>55</v>
       </c>
@@ -2144,11 +2464,21 @@
       <c r="C32" t="s">
         <v>71</v>
       </c>
-      <c r="D32"/>
-      <c r="E32"/>
-      <c r="F32"/>
-      <c r="G32"/>
-      <c r="H32"/>
+      <c r="D32" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E32" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F32" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G32" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H32" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I32" t="s">
         <v>55</v>
       </c>
@@ -2163,11 +2493,21 @@
       <c r="C33" t="s">
         <v>73</v>
       </c>
-      <c r="D33"/>
-      <c r="E33"/>
-      <c r="F33"/>
-      <c r="G33"/>
-      <c r="H33"/>
+      <c r="D33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H33" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I33" t="s">
         <v>55</v>
       </c>
@@ -2182,11 +2522,21 @@
       <c r="C34" t="s">
         <v>75</v>
       </c>
-      <c r="D34"/>
-      <c r="E34"/>
-      <c r="F34"/>
-      <c r="G34"/>
-      <c r="H34"/>
+      <c r="D34" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E34" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F34" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G34" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H34" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I34" t="s">
         <v>55</v>
       </c>
@@ -2201,11 +2551,21 @@
       <c r="C35" t="s">
         <v>77</v>
       </c>
-      <c r="D35"/>
-      <c r="E35"/>
-      <c r="F35"/>
-      <c r="G35"/>
-      <c r="H35"/>
+      <c r="D35" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E35" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F35" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G35" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H35" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I35" t="s">
         <v>55</v>
       </c>
@@ -2214,13 +2574,27 @@
       <c r="A36" t="s">
         <v>14</v>
       </c>
-      <c r="B36"/>
-      <c r="C36"/>
-      <c r="D36"/>
-      <c r="E36"/>
-      <c r="F36"/>
-      <c r="G36"/>
-      <c r="H36"/>
+      <c r="B36" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C36" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D36" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E36" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F36" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G36" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H36" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I36" t="s">
         <v>55</v>
       </c>
@@ -2235,11 +2609,21 @@
       <c r="C37" t="s">
         <v>79</v>
       </c>
-      <c r="D37"/>
-      <c r="E37"/>
-      <c r="F37"/>
-      <c r="G37"/>
-      <c r="H37"/>
+      <c r="D37" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E37" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F37" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G37" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H37" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I37" t="s">
         <v>18</v>
       </c>
@@ -2251,12 +2635,24 @@
       <c r="B38" t="s">
         <v>80</v>
       </c>
-      <c r="C38"/>
-      <c r="D38"/>
-      <c r="E38"/>
-      <c r="F38"/>
-      <c r="G38"/>
-      <c r="H38"/>
+      <c r="C38" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D38" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E38" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F38" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G38" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H38" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I38" t="s">
         <v>81</v>
       </c>
@@ -2271,11 +2667,21 @@
       <c r="C39" t="s">
         <v>83</v>
       </c>
-      <c r="D39"/>
-      <c r="E39"/>
-      <c r="F39"/>
-      <c r="G39"/>
-      <c r="H39"/>
+      <c r="D39" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E39" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F39" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G39" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H39" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I39" t="s">
         <v>81</v>
       </c>
@@ -2290,11 +2696,21 @@
       <c r="C40" t="s">
         <v>85</v>
       </c>
-      <c r="D40"/>
-      <c r="E40"/>
-      <c r="F40"/>
-      <c r="G40"/>
-      <c r="H40"/>
+      <c r="D40" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E40" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F40" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G40" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H40" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I40" t="s">
         <v>81</v>
       </c>
@@ -2309,11 +2725,21 @@
       <c r="C41" t="s">
         <v>87</v>
       </c>
-      <c r="D41"/>
-      <c r="E41"/>
-      <c r="F41"/>
-      <c r="G41"/>
-      <c r="H41"/>
+      <c r="D41" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E41" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F41" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G41" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H41" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I41" t="s">
         <v>81</v>
       </c>
@@ -2322,13 +2748,27 @@
       <c r="A42" t="s">
         <v>14</v>
       </c>
-      <c r="B42"/>
-      <c r="C42"/>
-      <c r="D42"/>
-      <c r="E42"/>
-      <c r="F42"/>
-      <c r="G42"/>
-      <c r="H42"/>
+      <c r="B42" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C42" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D42" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E42" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F42" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G42" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H42" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I42" t="s">
         <v>81</v>
       </c>
@@ -2343,11 +2783,21 @@
       <c r="C43" t="s">
         <v>89</v>
       </c>
-      <c r="D43"/>
-      <c r="E43"/>
-      <c r="F43"/>
-      <c r="G43"/>
-      <c r="H43"/>
+      <c r="D43" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E43" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F43" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G43" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H43" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I43" t="s">
         <v>18</v>
       </c>
@@ -2359,12 +2809,24 @@
       <c r="B44" t="s">
         <v>90</v>
       </c>
-      <c r="C44"/>
-      <c r="D44"/>
-      <c r="E44"/>
-      <c r="F44"/>
-      <c r="G44"/>
-      <c r="H44"/>
+      <c r="C44" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D44" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E44" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F44" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G44" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H44" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I44" t="s">
         <v>91</v>
       </c>
@@ -2379,11 +2841,21 @@
       <c r="C45" t="s">
         <v>93</v>
       </c>
-      <c r="D45"/>
-      <c r="E45"/>
-      <c r="F45"/>
-      <c r="G45"/>
-      <c r="H45"/>
+      <c r="D45" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E45" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F45" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G45" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H45" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I45" t="s">
         <v>91</v>
       </c>
@@ -2398,11 +2870,21 @@
       <c r="C46" t="s">
         <v>95</v>
       </c>
-      <c r="D46"/>
-      <c r="E46"/>
-      <c r="F46"/>
-      <c r="G46"/>
-      <c r="H46"/>
+      <c r="D46" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E46" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F46" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G46" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H46" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I46" t="s">
         <v>91</v>
       </c>
@@ -2417,11 +2899,21 @@
       <c r="C47" t="s">
         <v>97</v>
       </c>
-      <c r="D47"/>
-      <c r="E47"/>
-      <c r="F47"/>
-      <c r="G47"/>
-      <c r="H47"/>
+      <c r="D47" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E47" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F47" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G47" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H47" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I47" t="s">
         <v>91</v>
       </c>
@@ -2436,11 +2928,21 @@
       <c r="C48" t="s">
         <v>99</v>
       </c>
-      <c r="D48"/>
-      <c r="E48"/>
-      <c r="F48"/>
-      <c r="G48"/>
-      <c r="H48"/>
+      <c r="D48" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E48" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F48" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G48" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H48" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I48" t="s">
         <v>91</v>
       </c>
@@ -2455,11 +2957,21 @@
       <c r="C49" t="s">
         <v>101</v>
       </c>
-      <c r="D49"/>
-      <c r="E49"/>
-      <c r="F49"/>
-      <c r="G49"/>
-      <c r="H49"/>
+      <c r="D49" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E49" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F49" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G49" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H49" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I49" t="s">
         <v>91</v>
       </c>
@@ -2468,13 +2980,27 @@
       <c r="A50" t="s">
         <v>14</v>
       </c>
-      <c r="B50"/>
-      <c r="C50"/>
-      <c r="D50"/>
-      <c r="E50"/>
-      <c r="F50"/>
-      <c r="G50"/>
-      <c r="H50"/>
+      <c r="B50" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C50" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D50" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E50" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F50" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G50" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H50" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I50" t="s">
         <v>91</v>
       </c>
@@ -2486,12 +3012,24 @@
       <c r="B51" t="s">
         <v>102</v>
       </c>
-      <c r="C51"/>
-      <c r="D51"/>
-      <c r="E51"/>
-      <c r="F51"/>
-      <c r="G51"/>
-      <c r="H51"/>
+      <c r="C51" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D51" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E51" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F51" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G51" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H51" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I51" t="s">
         <v>103</v>
       </c>
@@ -2506,11 +3044,21 @@
       <c r="C52" t="s">
         <v>105</v>
       </c>
-      <c r="D52"/>
-      <c r="E52"/>
-      <c r="F52"/>
-      <c r="G52"/>
-      <c r="H52"/>
+      <c r="D52" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E52" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F52" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G52" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H52" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I52" t="s">
         <v>103</v>
       </c>
@@ -2525,11 +3073,21 @@
       <c r="C53" t="s">
         <v>107</v>
       </c>
-      <c r="D53"/>
-      <c r="E53"/>
-      <c r="F53"/>
-      <c r="G53"/>
-      <c r="H53"/>
+      <c r="D53" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E53" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F53" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G53" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H53" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I53" t="s">
         <v>103</v>
       </c>
@@ -2544,11 +3102,21 @@
       <c r="C54" t="s">
         <v>109</v>
       </c>
-      <c r="D54"/>
-      <c r="E54"/>
-      <c r="F54"/>
-      <c r="G54"/>
-      <c r="H54"/>
+      <c r="D54" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E54" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F54" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G54" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H54" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I54" t="s">
         <v>103</v>
       </c>
@@ -2563,11 +3131,21 @@
       <c r="C55" t="s">
         <v>111</v>
       </c>
-      <c r="D55"/>
-      <c r="E55"/>
-      <c r="F55"/>
-      <c r="G55"/>
-      <c r="H55"/>
+      <c r="D55" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E55" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F55" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G55" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H55" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I55" t="s">
         <v>103</v>
       </c>
@@ -2582,11 +3160,21 @@
       <c r="C56" t="s">
         <v>113</v>
       </c>
-      <c r="D56"/>
-      <c r="E56"/>
-      <c r="F56"/>
-      <c r="G56"/>
-      <c r="H56"/>
+      <c r="D56" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E56" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F56" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G56" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H56" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I56" t="s">
         <v>103</v>
       </c>
@@ -2595,13 +3183,27 @@
       <c r="A57" t="s">
         <v>14</v>
       </c>
-      <c r="B57"/>
-      <c r="C57"/>
-      <c r="D57"/>
-      <c r="E57"/>
-      <c r="F57"/>
-      <c r="G57"/>
-      <c r="H57"/>
+      <c r="B57" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C57" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D57" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E57" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F57" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G57" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H57" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I57" t="s">
         <v>103</v>
       </c>
@@ -2616,11 +3218,21 @@
       <c r="C58" t="s">
         <v>115</v>
       </c>
-      <c r="D58"/>
-      <c r="E58"/>
-      <c r="F58"/>
-      <c r="G58"/>
-      <c r="H58"/>
+      <c r="D58" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E58" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F58" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G58" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H58" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I58" t="s">
         <v>18</v>
       </c>
@@ -2632,12 +3244,24 @@
       <c r="B59" t="s">
         <v>116</v>
       </c>
-      <c r="C59"/>
-      <c r="D59"/>
-      <c r="E59"/>
-      <c r="F59"/>
-      <c r="G59"/>
-      <c r="H59"/>
+      <c r="C59" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D59" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E59" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F59" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G59" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H59" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I59" t="s">
         <v>117</v>
       </c>
@@ -2652,11 +3276,21 @@
       <c r="C60" t="s">
         <v>119</v>
       </c>
-      <c r="D60"/>
-      <c r="E60"/>
-      <c r="F60"/>
-      <c r="G60"/>
-      <c r="H60"/>
+      <c r="D60" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E60" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F60" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G60" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H60" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I60" t="s">
         <v>117</v>
       </c>
@@ -2671,11 +3305,21 @@
       <c r="C61" t="s">
         <v>121</v>
       </c>
-      <c r="D61"/>
-      <c r="E61"/>
-      <c r="F61"/>
-      <c r="G61"/>
-      <c r="H61"/>
+      <c r="D61" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E61" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F61" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G61" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H61" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I61" t="s">
         <v>117</v>
       </c>
@@ -2684,13 +3328,27 @@
       <c r="A62" t="s">
         <v>14</v>
       </c>
-      <c r="B62"/>
-      <c r="C62"/>
-      <c r="D62"/>
-      <c r="E62"/>
-      <c r="F62"/>
-      <c r="G62"/>
-      <c r="H62"/>
+      <c r="B62" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C62" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D62" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E62" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F62" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G62" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H62" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I62" t="s">
         <v>117</v>
       </c>
@@ -2702,12 +3360,24 @@
       <c r="B63" t="s">
         <v>122</v>
       </c>
-      <c r="C63"/>
-      <c r="D63"/>
-      <c r="E63"/>
-      <c r="F63"/>
-      <c r="G63"/>
-      <c r="H63"/>
+      <c r="C63" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D63" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E63" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F63" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G63" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H63" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I63" t="s">
         <v>123</v>
       </c>
@@ -2722,11 +3392,21 @@
       <c r="C64" t="s">
         <v>125</v>
       </c>
-      <c r="D64"/>
-      <c r="E64"/>
-      <c r="F64"/>
-      <c r="G64"/>
-      <c r="H64"/>
+      <c r="D64" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E64" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F64" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G64" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H64" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I64" t="s">
         <v>123</v>
       </c>
@@ -2741,11 +3421,21 @@
       <c r="C65" t="s">
         <v>127</v>
       </c>
-      <c r="D65"/>
-      <c r="E65"/>
-      <c r="F65"/>
-      <c r="G65"/>
-      <c r="H65"/>
+      <c r="D65" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E65" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F65" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G65" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H65" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I65" t="s">
         <v>123</v>
       </c>
@@ -2760,11 +3450,21 @@
       <c r="C66" t="s">
         <v>129</v>
       </c>
-      <c r="D66"/>
-      <c r="E66"/>
-      <c r="F66"/>
-      <c r="G66"/>
-      <c r="H66"/>
+      <c r="D66" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E66" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F66" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G66" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H66" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I66" t="s">
         <v>123</v>
       </c>
@@ -2773,13 +3473,27 @@
       <c r="A67" t="s">
         <v>14</v>
       </c>
-      <c r="B67"/>
-      <c r="C67"/>
-      <c r="D67"/>
-      <c r="E67"/>
-      <c r="F67"/>
-      <c r="G67"/>
-      <c r="H67"/>
+      <c r="B67" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C67" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D67" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E67" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F67" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G67" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H67" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I67" t="s">
         <v>123</v>
       </c>
@@ -2794,11 +3508,21 @@
       <c r="C68" t="s">
         <v>131</v>
       </c>
-      <c r="D68"/>
-      <c r="E68"/>
-      <c r="F68"/>
-      <c r="G68"/>
-      <c r="H68"/>
+      <c r="D68" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E68" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F68" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G68" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H68" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I68" t="s">
         <v>18</v>
       </c>
@@ -2810,12 +3534,24 @@
       <c r="B69" t="s">
         <v>132</v>
       </c>
-      <c r="C69"/>
-      <c r="D69"/>
-      <c r="E69"/>
-      <c r="F69"/>
-      <c r="G69"/>
-      <c r="H69"/>
+      <c r="C69" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D69" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E69" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F69" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G69" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H69" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I69" t="s">
         <v>133</v>
       </c>
@@ -2830,11 +3566,21 @@
       <c r="C70" t="s">
         <v>135</v>
       </c>
-      <c r="D70"/>
-      <c r="E70"/>
-      <c r="F70"/>
-      <c r="G70"/>
-      <c r="H70"/>
+      <c r="D70" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E70" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F70" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G70" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H70" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I70" t="s">
         <v>133</v>
       </c>
@@ -2849,11 +3595,21 @@
       <c r="C71" t="s">
         <v>137</v>
       </c>
-      <c r="D71"/>
-      <c r="E71"/>
-      <c r="F71"/>
-      <c r="G71"/>
-      <c r="H71"/>
+      <c r="D71" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E71" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F71" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G71" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H71" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I71" t="s">
         <v>133</v>
       </c>
@@ -2868,11 +3624,21 @@
       <c r="C72" t="s">
         <v>139</v>
       </c>
-      <c r="D72"/>
-      <c r="E72"/>
-      <c r="F72"/>
-      <c r="G72"/>
-      <c r="H72"/>
+      <c r="D72" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E72" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F72" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G72" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H72" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I72" t="s">
         <v>133</v>
       </c>
@@ -2887,11 +3653,21 @@
       <c r="C73" t="s">
         <v>141</v>
       </c>
-      <c r="D73"/>
-      <c r="E73"/>
-      <c r="F73"/>
-      <c r="G73"/>
-      <c r="H73"/>
+      <c r="D73" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E73" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F73" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G73" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H73" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I73" t="s">
         <v>133</v>
       </c>
@@ -2900,13 +3676,27 @@
       <c r="A74" t="s">
         <v>14</v>
       </c>
-      <c r="B74"/>
-      <c r="C74"/>
-      <c r="D74"/>
-      <c r="E74"/>
-      <c r="F74"/>
-      <c r="G74"/>
-      <c r="H74"/>
+      <c r="B74" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C74" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D74" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E74" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F74" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G74" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H74" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I74" t="s">
         <v>133</v>
       </c>
@@ -2918,12 +3708,24 @@
       <c r="B75" t="s">
         <v>142</v>
       </c>
-      <c r="C75"/>
-      <c r="D75"/>
-      <c r="E75"/>
-      <c r="F75"/>
-      <c r="G75"/>
-      <c r="H75"/>
+      <c r="C75" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D75" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E75" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F75" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G75" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H75" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I75" t="s">
         <v>143</v>
       </c>
@@ -2938,11 +3740,21 @@
       <c r="C76" t="s">
         <v>145</v>
       </c>
-      <c r="D76"/>
-      <c r="E76"/>
-      <c r="F76"/>
-      <c r="G76"/>
-      <c r="H76"/>
+      <c r="D76" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E76" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F76" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G76" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H76" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I76" t="s">
         <v>143</v>
       </c>
@@ -2957,11 +3769,21 @@
       <c r="C77" t="s">
         <v>147</v>
       </c>
-      <c r="D77"/>
-      <c r="E77"/>
-      <c r="F77"/>
-      <c r="G77"/>
-      <c r="H77"/>
+      <c r="D77" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E77" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F77" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G77" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H77" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I77" t="s">
         <v>143</v>
       </c>
@@ -2976,11 +3798,21 @@
       <c r="C78" t="s">
         <v>149</v>
       </c>
-      <c r="D78"/>
-      <c r="E78"/>
-      <c r="F78"/>
-      <c r="G78"/>
-      <c r="H78"/>
+      <c r="D78" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E78" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F78" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G78" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H78" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I78" t="s">
         <v>143</v>
       </c>
@@ -2989,13 +3821,27 @@
       <c r="A79" t="s">
         <v>14</v>
       </c>
-      <c r="B79"/>
-      <c r="C79"/>
-      <c r="D79"/>
-      <c r="E79"/>
-      <c r="F79"/>
-      <c r="G79"/>
-      <c r="H79"/>
+      <c r="B79" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C79" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D79" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E79" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F79" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G79" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H79" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I79" t="s">
         <v>143</v>
       </c>
@@ -3007,12 +3853,24 @@
       <c r="B80" t="s">
         <v>150</v>
       </c>
-      <c r="C80"/>
-      <c r="D80"/>
-      <c r="E80"/>
-      <c r="F80"/>
-      <c r="G80"/>
-      <c r="H80"/>
+      <c r="C80" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D80" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E80" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F80" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G80" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H80" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I80" t="s">
         <v>151</v>
       </c>
@@ -3027,11 +3885,21 @@
       <c r="C81" t="s">
         <v>153</v>
       </c>
-      <c r="D81"/>
-      <c r="E81"/>
-      <c r="F81"/>
-      <c r="G81"/>
-      <c r="H81"/>
+      <c r="D81" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E81" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F81" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G81" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H81" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I81" t="s">
         <v>151</v>
       </c>
@@ -3046,11 +3914,21 @@
       <c r="C82" t="s">
         <v>155</v>
       </c>
-      <c r="D82"/>
-      <c r="E82"/>
-      <c r="F82"/>
-      <c r="G82"/>
-      <c r="H82"/>
+      <c r="D82" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E82" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F82" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G82" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H82" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I82" t="s">
         <v>151</v>
       </c>
@@ -3065,11 +3943,21 @@
       <c r="C83" t="s">
         <v>157</v>
       </c>
-      <c r="D83"/>
-      <c r="E83"/>
-      <c r="F83"/>
-      <c r="G83"/>
-      <c r="H83"/>
+      <c r="D83" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E83" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F83" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G83" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H83" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I83" t="s">
         <v>151</v>
       </c>
@@ -3084,11 +3972,21 @@
       <c r="C84" t="s">
         <v>159</v>
       </c>
-      <c r="D84"/>
-      <c r="E84"/>
-      <c r="F84"/>
-      <c r="G84"/>
-      <c r="H84"/>
+      <c r="D84" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E84" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F84" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G84" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H84" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I84" t="s">
         <v>151</v>
       </c>
@@ -3097,13 +3995,27 @@
       <c r="A85" t="s">
         <v>14</v>
       </c>
-      <c r="B85"/>
-      <c r="C85"/>
-      <c r="D85"/>
-      <c r="E85"/>
-      <c r="F85"/>
-      <c r="G85"/>
-      <c r="H85"/>
+      <c r="B85" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C85" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D85" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E85" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F85" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G85" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H85" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I85" t="s">
         <v>151</v>
       </c>
@@ -3118,11 +4030,21 @@
       <c r="C86" t="s">
         <v>161</v>
       </c>
-      <c r="D86"/>
-      <c r="E86"/>
-      <c r="F86"/>
-      <c r="G86"/>
-      <c r="H86"/>
+      <c r="D86" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E86" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F86" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G86" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H86" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I86" t="s">
         <v>162</v>
       </c>
@@ -3137,11 +4059,21 @@
       <c r="C87" t="s">
         <v>164</v>
       </c>
-      <c r="D87"/>
-      <c r="E87"/>
-      <c r="F87"/>
-      <c r="G87"/>
-      <c r="H87"/>
+      <c r="D87" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E87" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F87" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G87" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H87" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I87" t="s">
         <v>162</v>
       </c>
@@ -3156,11 +4088,21 @@
       <c r="C88" t="s">
         <v>161</v>
       </c>
-      <c r="D88"/>
-      <c r="E88"/>
-      <c r="F88"/>
-      <c r="G88"/>
-      <c r="H88"/>
+      <c r="D88" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E88" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F88" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G88" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H88" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I88" t="s">
         <v>162</v>
       </c>
@@ -3175,11 +4117,21 @@
       <c r="C89" t="s">
         <v>167</v>
       </c>
-      <c r="D89"/>
-      <c r="E89"/>
-      <c r="F89"/>
-      <c r="G89"/>
-      <c r="H89"/>
+      <c r="D89" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E89" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F89" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G89" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H89" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I89" t="s">
         <v>162</v>
       </c>
@@ -3194,11 +4146,21 @@
       <c r="C90" t="s">
         <v>169</v>
       </c>
-      <c r="D90"/>
-      <c r="E90"/>
-      <c r="F90"/>
-      <c r="G90"/>
-      <c r="H90"/>
+      <c r="D90" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E90" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F90" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G90" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H90" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I90" t="s">
         <v>162</v>
       </c>
@@ -3207,13 +4169,27 @@
       <c r="A91" t="s">
         <v>14</v>
       </c>
-      <c r="B91"/>
-      <c r="C91"/>
-      <c r="D91"/>
-      <c r="E91"/>
-      <c r="F91"/>
-      <c r="G91"/>
-      <c r="H91"/>
+      <c r="B91" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C91" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D91" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E91" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F91" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G91" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H91" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I91" t="s">
         <v>162</v>
       </c>
@@ -3225,12 +4201,24 @@
       <c r="B92" t="s">
         <v>170</v>
       </c>
-      <c r="C92"/>
-      <c r="D92"/>
-      <c r="E92"/>
-      <c r="F92"/>
-      <c r="G92"/>
-      <c r="H92"/>
+      <c r="C92" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D92" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E92" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F92" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G92" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H92" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I92" t="s">
         <v>171</v>
       </c>
@@ -3245,11 +4233,21 @@
       <c r="C93" t="s">
         <v>173</v>
       </c>
-      <c r="D93"/>
-      <c r="E93"/>
-      <c r="F93"/>
-      <c r="G93"/>
-      <c r="H93"/>
+      <c r="D93" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E93" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F93" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G93" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H93" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I93" t="s">
         <v>171</v>
       </c>
@@ -3264,11 +4262,21 @@
       <c r="C94" t="s">
         <v>175</v>
       </c>
-      <c r="D94"/>
-      <c r="E94"/>
-      <c r="F94"/>
-      <c r="G94"/>
-      <c r="H94"/>
+      <c r="D94" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E94" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F94" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G94" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H94" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I94" t="s">
         <v>171</v>
       </c>
@@ -3283,11 +4291,21 @@
       <c r="C95" t="s">
         <v>177</v>
       </c>
-      <c r="D95"/>
-      <c r="E95"/>
-      <c r="F95"/>
-      <c r="G95"/>
-      <c r="H95"/>
+      <c r="D95" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E95" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F95" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G95" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H95" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I95" t="s">
         <v>171</v>
       </c>
@@ -3296,13 +4314,27 @@
       <c r="A96" t="s">
         <v>14</v>
       </c>
-      <c r="B96"/>
-      <c r="C96"/>
-      <c r="D96"/>
-      <c r="E96"/>
-      <c r="F96"/>
-      <c r="G96"/>
-      <c r="H96"/>
+      <c r="B96" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C96" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D96" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E96" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F96" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G96" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H96" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I96" t="s">
         <v>171</v>
       </c>
@@ -3317,11 +4349,21 @@
       <c r="C97" t="s">
         <v>179</v>
       </c>
-      <c r="D97"/>
-      <c r="E97"/>
-      <c r="F97"/>
-      <c r="G97"/>
-      <c r="H97"/>
+      <c r="D97" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E97" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F97" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G97" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H97" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I97" t="s">
         <v>18</v>
       </c>
@@ -3336,11 +4378,21 @@
       <c r="C98" t="s">
         <v>181</v>
       </c>
-      <c r="D98"/>
-      <c r="E98"/>
-      <c r="F98"/>
-      <c r="G98"/>
-      <c r="H98"/>
+      <c r="D98" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E98" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F98" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G98" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H98" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I98" t="s">
         <v>18</v>
       </c>
@@ -3352,12 +4404,24 @@
       <c r="B99" t="s">
         <v>182</v>
       </c>
-      <c r="C99"/>
-      <c r="D99"/>
-      <c r="E99"/>
-      <c r="F99"/>
-      <c r="G99"/>
-      <c r="H99"/>
+      <c r="C99" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D99" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E99" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F99" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G99" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H99" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I99" t="s">
         <v>183</v>
       </c>
@@ -3372,11 +4436,21 @@
       <c r="C100" t="s">
         <v>185</v>
       </c>
-      <c r="D100"/>
-      <c r="E100"/>
-      <c r="F100"/>
-      <c r="G100"/>
-      <c r="H100"/>
+      <c r="D100" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E100" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F100" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G100" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H100" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I100" t="s">
         <v>183</v>
       </c>
@@ -3391,11 +4465,21 @@
       <c r="C101" t="s">
         <v>187</v>
       </c>
-      <c r="D101"/>
-      <c r="E101"/>
-      <c r="F101"/>
-      <c r="G101"/>
-      <c r="H101"/>
+      <c r="D101" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E101" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F101" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G101" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H101" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I101" t="s">
         <v>183</v>
       </c>
@@ -3410,11 +4494,21 @@
       <c r="C102" t="s">
         <v>189</v>
       </c>
-      <c r="D102"/>
-      <c r="E102"/>
-      <c r="F102"/>
-      <c r="G102"/>
-      <c r="H102"/>
+      <c r="D102" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E102" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F102" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G102" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H102" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I102" t="s">
         <v>183</v>
       </c>
@@ -3429,11 +4523,21 @@
       <c r="C103" t="s">
         <v>191</v>
       </c>
-      <c r="D103"/>
-      <c r="E103"/>
-      <c r="F103"/>
-      <c r="G103"/>
-      <c r="H103"/>
+      <c r="D103" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E103" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F103" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G103" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H103" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I103" t="s">
         <v>183</v>
       </c>
@@ -3448,11 +4552,21 @@
       <c r="C104" t="s">
         <v>193</v>
       </c>
-      <c r="D104"/>
-      <c r="E104"/>
-      <c r="F104"/>
-      <c r="G104"/>
-      <c r="H104"/>
+      <c r="D104" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E104" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F104" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G104" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H104" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I104" t="s">
         <v>183</v>
       </c>
@@ -3461,13 +4575,27 @@
       <c r="A105" t="s">
         <v>14</v>
       </c>
-      <c r="B105"/>
-      <c r="C105"/>
-      <c r="D105"/>
-      <c r="E105"/>
-      <c r="F105"/>
-      <c r="G105"/>
-      <c r="H105"/>
+      <c r="B105" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C105" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D105" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E105" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F105" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G105" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H105" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I105" t="s">
         <v>183</v>
       </c>
@@ -3482,11 +4610,21 @@
       <c r="C106" t="s">
         <v>195</v>
       </c>
-      <c r="D106"/>
-      <c r="E106"/>
-      <c r="F106"/>
-      <c r="G106"/>
-      <c r="H106"/>
+      <c r="D106" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E106" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F106" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G106" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H106" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I106" t="s">
         <v>18</v>
       </c>
@@ -3498,12 +4636,24 @@
       <c r="B107" t="s">
         <v>196</v>
       </c>
-      <c r="C107"/>
-      <c r="D107"/>
-      <c r="E107"/>
-      <c r="F107"/>
-      <c r="G107"/>
-      <c r="H107"/>
+      <c r="C107" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D107" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E107" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F107" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G107" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H107" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I107" t="s">
         <v>197</v>
       </c>
@@ -3518,11 +4668,21 @@
       <c r="C108" t="s">
         <v>199</v>
       </c>
-      <c r="D108"/>
-      <c r="E108"/>
-      <c r="F108"/>
-      <c r="G108"/>
-      <c r="H108"/>
+      <c r="D108" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E108" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F108" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G108" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H108" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I108" t="s">
         <v>197</v>
       </c>
@@ -3537,11 +4697,21 @@
       <c r="C109" t="s">
         <v>201</v>
       </c>
-      <c r="D109"/>
-      <c r="E109"/>
-      <c r="F109"/>
-      <c r="G109"/>
-      <c r="H109"/>
+      <c r="D109" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E109" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F109" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G109" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H109" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I109" t="s">
         <v>197</v>
       </c>
@@ -3550,13 +4720,27 @@
       <c r="A110" t="s">
         <v>14</v>
       </c>
-      <c r="B110"/>
-      <c r="C110"/>
-      <c r="D110"/>
-      <c r="E110"/>
-      <c r="F110"/>
-      <c r="G110"/>
-      <c r="H110"/>
+      <c r="B110" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C110" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D110" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E110" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F110" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G110" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H110" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I110" t="s">
         <v>197</v>
       </c>
@@ -3568,12 +4752,24 @@
       <c r="B111" t="s">
         <v>202</v>
       </c>
-      <c r="C111"/>
-      <c r="D111"/>
-      <c r="E111"/>
-      <c r="F111"/>
-      <c r="G111"/>
-      <c r="H111"/>
+      <c r="C111" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D111" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E111" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F111" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G111" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H111" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I111" t="s">
         <v>203</v>
       </c>
@@ -3588,11 +4784,21 @@
       <c r="C112" t="s">
         <v>205</v>
       </c>
-      <c r="D112"/>
-      <c r="E112"/>
-      <c r="F112"/>
-      <c r="G112"/>
-      <c r="H112"/>
+      <c r="D112" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E112" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F112" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G112" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H112" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I112" t="s">
         <v>203</v>
       </c>
@@ -3607,11 +4813,21 @@
       <c r="C113" t="s">
         <v>207</v>
       </c>
-      <c r="D113"/>
-      <c r="E113"/>
-      <c r="F113"/>
-      <c r="G113"/>
-      <c r="H113"/>
+      <c r="D113" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E113" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F113" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G113" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H113" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I113" t="s">
         <v>203</v>
       </c>
@@ -3626,11 +4842,21 @@
       <c r="C114" t="s">
         <v>209</v>
       </c>
-      <c r="D114"/>
-      <c r="E114"/>
-      <c r="F114"/>
-      <c r="G114"/>
-      <c r="H114"/>
+      <c r="D114" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E114" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F114" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G114" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H114" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I114" t="s">
         <v>203</v>
       </c>
@@ -3645,11 +4871,21 @@
       <c r="C115" t="s">
         <v>211</v>
       </c>
-      <c r="D115"/>
-      <c r="E115"/>
-      <c r="F115"/>
-      <c r="G115"/>
-      <c r="H115"/>
+      <c r="D115" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E115" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F115" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G115" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H115" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I115" t="s">
         <v>203</v>
       </c>
@@ -3664,11 +4900,21 @@
       <c r="C116" t="s">
         <v>213</v>
       </c>
-      <c r="D116"/>
-      <c r="E116"/>
-      <c r="F116"/>
-      <c r="G116"/>
-      <c r="H116"/>
+      <c r="D116" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E116" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F116" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G116" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H116" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I116" t="s">
         <v>203</v>
       </c>
@@ -3683,11 +4929,21 @@
       <c r="C117" t="s">
         <v>215</v>
       </c>
-      <c r="D117"/>
-      <c r="E117"/>
-      <c r="F117"/>
-      <c r="G117"/>
-      <c r="H117"/>
+      <c r="D117" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E117" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F117" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G117" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H117" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I117" t="s">
         <v>203</v>
       </c>
@@ -3702,11 +4958,21 @@
       <c r="C118" t="s">
         <v>217</v>
       </c>
-      <c r="D118"/>
-      <c r="E118"/>
-      <c r="F118"/>
-      <c r="G118"/>
-      <c r="H118"/>
+      <c r="D118" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E118" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F118" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G118" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H118" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I118" t="s">
         <v>203</v>
       </c>
@@ -3721,11 +4987,21 @@
       <c r="C119" t="s">
         <v>219</v>
       </c>
-      <c r="D119"/>
-      <c r="E119"/>
-      <c r="F119"/>
-      <c r="G119"/>
-      <c r="H119"/>
+      <c r="D119" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E119" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F119" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G119" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H119" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I119" t="s">
         <v>203</v>
       </c>
@@ -3740,11 +5016,21 @@
       <c r="C120" t="s">
         <v>221</v>
       </c>
-      <c r="D120"/>
-      <c r="E120"/>
-      <c r="F120"/>
-      <c r="G120"/>
-      <c r="H120"/>
+      <c r="D120" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E120" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F120" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G120" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H120" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I120" t="s">
         <v>203</v>
       </c>
@@ -3753,13 +5039,27 @@
       <c r="A121" t="s">
         <v>14</v>
       </c>
-      <c r="B121"/>
-      <c r="C121"/>
-      <c r="D121"/>
-      <c r="E121"/>
-      <c r="F121"/>
-      <c r="G121"/>
-      <c r="H121"/>
+      <c r="B121" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C121" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D121" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E121" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F121" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G121" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H121" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I121" t="s">
         <v>203</v>
       </c>
@@ -3771,12 +5071,24 @@
       <c r="B122" t="s">
         <v>222</v>
       </c>
-      <c r="C122"/>
-      <c r="D122"/>
-      <c r="E122"/>
-      <c r="F122"/>
-      <c r="G122"/>
-      <c r="H122"/>
+      <c r="C122" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D122" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E122" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F122" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G122" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H122" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I122" t="s">
         <v>223</v>
       </c>
@@ -3791,11 +5103,21 @@
       <c r="C123" t="s">
         <v>225</v>
       </c>
-      <c r="D123"/>
-      <c r="E123"/>
-      <c r="F123"/>
-      <c r="G123"/>
-      <c r="H123"/>
+      <c r="D123" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E123" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F123" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G123" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H123" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I123" t="s">
         <v>223</v>
       </c>
@@ -3810,11 +5132,21 @@
       <c r="C124" t="s">
         <v>227</v>
       </c>
-      <c r="D124"/>
-      <c r="E124"/>
-      <c r="F124"/>
-      <c r="G124"/>
-      <c r="H124"/>
+      <c r="D124" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E124" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F124" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G124" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H124" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I124" t="s">
         <v>223</v>
       </c>
@@ -3829,11 +5161,21 @@
       <c r="C125" t="s">
         <v>229</v>
       </c>
-      <c r="D125"/>
-      <c r="E125"/>
-      <c r="F125"/>
-      <c r="G125"/>
-      <c r="H125"/>
+      <c r="D125" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E125" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F125" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G125" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H125" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I125" t="s">
         <v>223</v>
       </c>
@@ -3848,11 +5190,21 @@
       <c r="C126" t="s">
         <v>231</v>
       </c>
-      <c r="D126"/>
-      <c r="E126"/>
-      <c r="F126"/>
-      <c r="G126"/>
-      <c r="H126"/>
+      <c r="D126" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E126" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F126" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G126" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H126" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I126" t="s">
         <v>223</v>
       </c>
@@ -3867,11 +5219,21 @@
       <c r="C127" t="s">
         <v>233</v>
       </c>
-      <c r="D127"/>
-      <c r="E127"/>
-      <c r="F127"/>
-      <c r="G127"/>
-      <c r="H127"/>
+      <c r="D127" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E127" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F127" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G127" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H127" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I127" t="s">
         <v>223</v>
       </c>
@@ -3880,13 +5242,27 @@
       <c r="A128" t="s">
         <v>14</v>
       </c>
-      <c r="B128"/>
-      <c r="C128"/>
-      <c r="D128"/>
-      <c r="E128"/>
-      <c r="F128"/>
-      <c r="G128"/>
-      <c r="H128"/>
+      <c r="B128" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C128" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D128" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E128" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F128" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G128" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H128" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I128" t="s">
         <v>223</v>
       </c>
@@ -3901,11 +5277,21 @@
       <c r="C129" t="s">
         <v>20</v>
       </c>
-      <c r="D129"/>
-      <c r="E129"/>
-      <c r="F129"/>
-      <c r="G129"/>
-      <c r="H129"/>
+      <c r="D129" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E129" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F129" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G129" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H129" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I129" t="s">
         <v>19</v>
       </c>
@@ -3920,11 +5306,21 @@
       <c r="C130" t="s">
         <v>236</v>
       </c>
-      <c r="D130"/>
-      <c r="E130"/>
-      <c r="F130"/>
-      <c r="G130"/>
-      <c r="H130"/>
+      <c r="D130" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E130" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F130" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G130" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H130" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I130" t="s">
         <v>19</v>
       </c>
@@ -3939,11 +5335,21 @@
       <c r="C131" t="s">
         <v>239</v>
       </c>
-      <c r="D131"/>
-      <c r="E131"/>
-      <c r="F131"/>
-      <c r="G131"/>
-      <c r="H131"/>
+      <c r="D131" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E131" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F131" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G131" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H131" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I131" t="s">
         <v>19</v>
       </c>
@@ -3952,13 +5358,27 @@
       <c r="A132" t="s">
         <v>14</v>
       </c>
-      <c r="B132"/>
-      <c r="C132"/>
-      <c r="D132"/>
-      <c r="E132"/>
-      <c r="F132"/>
-      <c r="G132"/>
-      <c r="H132"/>
+      <c r="B132" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C132" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D132" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E132" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F132" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G132" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H132" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I132" t="s">
         <v>19</v>
       </c>
@@ -4405,7 +5825,9 @@
       <c r="H2" t="s">
         <v>12</v>
       </c>
-      <c r="I2"/>
+      <c r="I2" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="J2" t="s">
         <v>10</v>
       </c>
@@ -4430,8 +5852,12 @@
       <c r="Q2" t="s">
         <v>309</v>
       </c>
-      <c r="R2"/>
-      <c r="S2"/>
+      <c r="R2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S2" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -4485,8 +5911,12 @@
       <c r="Q3" t="s">
         <v>312</v>
       </c>
-      <c r="R3"/>
-      <c r="S3"/>
+      <c r="R3" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S3" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -4540,8 +5970,12 @@
       <c r="Q4" t="s">
         <v>309</v>
       </c>
-      <c r="R4"/>
-      <c r="S4"/>
+      <c r="R4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S4" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -4568,7 +6002,9 @@
       <c r="H5" t="s">
         <v>24</v>
       </c>
-      <c r="I5"/>
+      <c r="I5" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="J5" t="s">
         <v>18</v>
       </c>
@@ -4593,8 +6029,12 @@
       <c r="Q5" t="s">
         <v>314</v>
       </c>
-      <c r="R5"/>
-      <c r="S5"/>
+      <c r="R5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S5" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -4648,8 +6088,12 @@
       <c r="Q6" t="s">
         <v>312</v>
       </c>
-      <c r="R6"/>
-      <c r="S6"/>
+      <c r="R6" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S6" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -4703,8 +6147,12 @@
       <c r="Q7" t="s">
         <v>312</v>
       </c>
-      <c r="R7"/>
-      <c r="S7"/>
+      <c r="R7" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S7" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -4731,7 +6179,9 @@
       <c r="H8" t="s">
         <v>24</v>
       </c>
-      <c r="I8"/>
+      <c r="I8" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="J8" t="s">
         <v>18</v>
       </c>
@@ -4756,8 +6206,12 @@
       <c r="Q8" t="s">
         <v>314</v>
       </c>
-      <c r="R8"/>
-      <c r="S8"/>
+      <c r="R8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S8" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -4811,8 +6265,12 @@
       <c r="Q9" t="s">
         <v>312</v>
       </c>
-      <c r="R9"/>
-      <c r="S9"/>
+      <c r="R9" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S9" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -4866,8 +6324,12 @@
       <c r="Q10" t="s">
         <v>312</v>
       </c>
-      <c r="R10"/>
-      <c r="S10"/>
+      <c r="R10" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S10" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -4921,8 +6383,12 @@
       <c r="Q11" t="s">
         <v>312</v>
       </c>
-      <c r="R11"/>
-      <c r="S11"/>
+      <c r="R11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S11" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -4976,8 +6442,12 @@
       <c r="Q12" t="s">
         <v>312</v>
       </c>
-      <c r="R12"/>
-      <c r="S12"/>
+      <c r="R12" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S12" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -5031,8 +6501,12 @@
       <c r="Q13" t="s">
         <v>312</v>
       </c>
-      <c r="R13"/>
-      <c r="S13"/>
+      <c r="R13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S13" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -5086,8 +6560,12 @@
       <c r="Q14" t="s">
         <v>312</v>
       </c>
-      <c r="R14"/>
-      <c r="S14"/>
+      <c r="R14" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S14" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -5141,8 +6619,12 @@
       <c r="Q15" t="s">
         <v>312</v>
       </c>
-      <c r="R15"/>
-      <c r="S15"/>
+      <c r="R15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S15" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -5196,8 +6678,12 @@
       <c r="Q16" t="s">
         <v>312</v>
       </c>
-      <c r="R16"/>
-      <c r="S16"/>
+      <c r="R16" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S16" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -5251,8 +6737,12 @@
       <c r="Q17" t="s">
         <v>312</v>
       </c>
-      <c r="R17"/>
-      <c r="S17"/>
+      <c r="R17" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S17" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -5306,8 +6796,12 @@
       <c r="Q18" t="s">
         <v>312</v>
       </c>
-      <c r="R18"/>
-      <c r="S18"/>
+      <c r="R18" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S18" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -5361,8 +6855,12 @@
       <c r="Q19" t="s">
         <v>312</v>
       </c>
-      <c r="R19"/>
-      <c r="S19"/>
+      <c r="R19" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S19" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -5416,8 +6914,12 @@
       <c r="Q20" t="s">
         <v>312</v>
       </c>
-      <c r="R20"/>
-      <c r="S20"/>
+      <c r="R20" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S20" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -5471,8 +6973,12 @@
       <c r="Q21" t="s">
         <v>312</v>
       </c>
-      <c r="R21"/>
-      <c r="S21"/>
+      <c r="R21" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S21" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -5526,8 +7032,12 @@
       <c r="Q22" t="s">
         <v>312</v>
       </c>
-      <c r="R22"/>
-      <c r="S22"/>
+      <c r="R22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S22" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -5581,8 +7091,12 @@
       <c r="Q23" t="s">
         <v>312</v>
       </c>
-      <c r="R23"/>
-      <c r="S23"/>
+      <c r="R23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S23" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -5636,8 +7150,12 @@
       <c r="Q24" t="s">
         <v>312</v>
       </c>
-      <c r="R24"/>
-      <c r="S24"/>
+      <c r="R24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S24" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -5691,8 +7209,12 @@
       <c r="Q25" t="s">
         <v>312</v>
       </c>
-      <c r="R25"/>
-      <c r="S25"/>
+      <c r="R25" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S25" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -5746,8 +7268,12 @@
       <c r="Q26" t="s">
         <v>312</v>
       </c>
-      <c r="R26"/>
-      <c r="S26"/>
+      <c r="R26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S26" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -5801,8 +7327,12 @@
       <c r="Q27" t="s">
         <v>312</v>
       </c>
-      <c r="R27"/>
-      <c r="S27"/>
+      <c r="R27" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S27" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -5856,8 +7386,12 @@
       <c r="Q28" t="s">
         <v>312</v>
       </c>
-      <c r="R28"/>
-      <c r="S28"/>
+      <c r="R28" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S28" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -5911,8 +7445,12 @@
       <c r="Q29" t="s">
         <v>312</v>
       </c>
-      <c r="R29"/>
-      <c r="S29"/>
+      <c r="R29" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S29" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -5966,8 +7504,12 @@
       <c r="Q30" t="s">
         <v>312</v>
       </c>
-      <c r="R30"/>
-      <c r="S30"/>
+      <c r="R30" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S30" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -6021,8 +7563,12 @@
       <c r="Q31" t="s">
         <v>312</v>
       </c>
-      <c r="R31"/>
-      <c r="S31"/>
+      <c r="R31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S31" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -6076,8 +7622,12 @@
       <c r="Q32" t="s">
         <v>312</v>
       </c>
-      <c r="R32"/>
-      <c r="S32"/>
+      <c r="R32" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S32" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -6131,8 +7681,12 @@
       <c r="Q33" t="s">
         <v>312</v>
       </c>
-      <c r="R33"/>
-      <c r="S33"/>
+      <c r="R33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S33" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -6186,8 +7740,12 @@
       <c r="Q34" t="s">
         <v>312</v>
       </c>
-      <c r="R34"/>
-      <c r="S34"/>
+      <c r="R34" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S34" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -6241,8 +7799,12 @@
       <c r="Q35" t="s">
         <v>312</v>
       </c>
-      <c r="R35"/>
-      <c r="S35"/>
+      <c r="R35" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S35" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -6296,8 +7858,12 @@
       <c r="Q36" t="s">
         <v>312</v>
       </c>
-      <c r="R36"/>
-      <c r="S36"/>
+      <c r="R36" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S36" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -6351,8 +7917,12 @@
       <c r="Q37" t="s">
         <v>312</v>
       </c>
-      <c r="R37"/>
-      <c r="S37"/>
+      <c r="R37" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S37" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -6406,8 +7976,12 @@
       <c r="Q38" t="s">
         <v>312</v>
       </c>
-      <c r="R38"/>
-      <c r="S38"/>
+      <c r="R38" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S38" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -6461,8 +8035,12 @@
       <c r="Q39" t="s">
         <v>312</v>
       </c>
-      <c r="R39"/>
-      <c r="S39"/>
+      <c r="R39" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S39" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -6516,8 +8094,12 @@
       <c r="Q40" t="s">
         <v>312</v>
       </c>
-      <c r="R40"/>
-      <c r="S40"/>
+      <c r="R40" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S40" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -6571,8 +8153,12 @@
       <c r="Q41" t="s">
         <v>312</v>
       </c>
-      <c r="R41"/>
-      <c r="S41"/>
+      <c r="R41" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S41" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -6626,8 +8212,12 @@
       <c r="Q42" t="s">
         <v>312</v>
       </c>
-      <c r="R42"/>
-      <c r="S42"/>
+      <c r="R42" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S42" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -6681,8 +8271,12 @@
       <c r="Q43" t="s">
         <v>312</v>
       </c>
-      <c r="R43"/>
-      <c r="S43"/>
+      <c r="R43" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S43" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6736,8 +8330,12 @@
       <c r="Q44" t="s">
         <v>312</v>
       </c>
-      <c r="R44"/>
-      <c r="S44"/>
+      <c r="R44" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S44" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6791,8 +8389,12 @@
       <c r="Q45" t="s">
         <v>312</v>
       </c>
-      <c r="R45"/>
-      <c r="S45"/>
+      <c r="R45" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S45" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6846,8 +8448,12 @@
       <c r="Q46" t="s">
         <v>312</v>
       </c>
-      <c r="R46"/>
-      <c r="S46"/>
+      <c r="R46" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S46" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6901,8 +8507,12 @@
       <c r="Q47" t="s">
         <v>312</v>
       </c>
-      <c r="R47"/>
-      <c r="S47"/>
+      <c r="R47" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S47" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6956,8 +8566,12 @@
       <c r="Q48" t="s">
         <v>312</v>
       </c>
-      <c r="R48"/>
-      <c r="S48"/>
+      <c r="R48" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S48" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -7011,8 +8625,12 @@
       <c r="Q49" t="s">
         <v>312</v>
       </c>
-      <c r="R49"/>
-      <c r="S49"/>
+      <c r="R49" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S49" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -7066,8 +8684,12 @@
       <c r="Q50" t="s">
         <v>312</v>
       </c>
-      <c r="R50"/>
-      <c r="S50"/>
+      <c r="R50" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S50" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -7121,8 +8743,12 @@
       <c r="Q51" t="s">
         <v>312</v>
       </c>
-      <c r="R51"/>
-      <c r="S51"/>
+      <c r="R51" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S51" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -7176,8 +8802,12 @@
       <c r="Q52" t="s">
         <v>312</v>
       </c>
-      <c r="R52"/>
-      <c r="S52"/>
+      <c r="R52" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S52" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7231,8 +8861,12 @@
       <c r="Q53" t="s">
         <v>312</v>
       </c>
-      <c r="R53"/>
-      <c r="S53"/>
+      <c r="R53" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S53" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7286,8 +8920,12 @@
       <c r="Q54" t="s">
         <v>312</v>
       </c>
-      <c r="R54"/>
-      <c r="S54"/>
+      <c r="R54" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S54" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7341,8 +8979,12 @@
       <c r="Q55" t="s">
         <v>312</v>
       </c>
-      <c r="R55"/>
-      <c r="S55"/>
+      <c r="R55" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S55" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7396,8 +9038,12 @@
       <c r="Q56" t="s">
         <v>312</v>
       </c>
-      <c r="R56"/>
-      <c r="S56"/>
+      <c r="R56" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S56" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7451,8 +9097,12 @@
       <c r="Q57" t="s">
         <v>312</v>
       </c>
-      <c r="R57"/>
-      <c r="S57"/>
+      <c r="R57" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S57" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7506,8 +9156,12 @@
       <c r="Q58" t="s">
         <v>312</v>
       </c>
-      <c r="R58"/>
-      <c r="S58"/>
+      <c r="R58" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S58" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7561,8 +9215,12 @@
       <c r="Q59" t="s">
         <v>312</v>
       </c>
-      <c r="R59"/>
-      <c r="S59"/>
+      <c r="R59" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S59" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7616,8 +9274,12 @@
       <c r="Q60" t="s">
         <v>312</v>
       </c>
-      <c r="R60"/>
-      <c r="S60"/>
+      <c r="R60" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S60" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7671,8 +9333,12 @@
       <c r="Q61" t="s">
         <v>312</v>
       </c>
-      <c r="R61"/>
-      <c r="S61"/>
+      <c r="R61" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S61" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7726,8 +9392,12 @@
       <c r="Q62" t="s">
         <v>312</v>
       </c>
-      <c r="R62"/>
-      <c r="S62"/>
+      <c r="R62" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S62" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7781,8 +9451,12 @@
       <c r="Q63" t="s">
         <v>312</v>
       </c>
-      <c r="R63"/>
-      <c r="S63"/>
+      <c r="R63" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S63" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7836,8 +9510,12 @@
       <c r="Q64" t="s">
         <v>312</v>
       </c>
-      <c r="R64"/>
-      <c r="S64"/>
+      <c r="R64" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S64" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7891,8 +9569,12 @@
       <c r="Q65" t="s">
         <v>312</v>
       </c>
-      <c r="R65"/>
-      <c r="S65"/>
+      <c r="R65" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S65" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7946,8 +9628,12 @@
       <c r="Q66" t="s">
         <v>312</v>
       </c>
-      <c r="R66"/>
-      <c r="S66"/>
+      <c r="R66" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S66" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8001,8 +9687,12 @@
       <c r="Q67" t="s">
         <v>312</v>
       </c>
-      <c r="R67"/>
-      <c r="S67"/>
+      <c r="R67" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S67" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8056,8 +9746,12 @@
       <c r="Q68" t="s">
         <v>312</v>
       </c>
-      <c r="R68"/>
-      <c r="S68"/>
+      <c r="R68" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S68" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8111,8 +9805,12 @@
       <c r="Q69" t="s">
         <v>312</v>
       </c>
-      <c r="R69"/>
-      <c r="S69"/>
+      <c r="R69" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S69" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8166,8 +9864,12 @@
       <c r="Q70" t="s">
         <v>312</v>
       </c>
-      <c r="R70"/>
-      <c r="S70"/>
+      <c r="R70" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S70" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8221,8 +9923,12 @@
       <c r="Q71" t="s">
         <v>312</v>
       </c>
-      <c r="R71"/>
-      <c r="S71"/>
+      <c r="R71" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S71" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8276,8 +9982,12 @@
       <c r="Q72" t="s">
         <v>312</v>
       </c>
-      <c r="R72"/>
-      <c r="S72"/>
+      <c r="R72" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S72" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8331,8 +10041,12 @@
       <c r="Q73" t="s">
         <v>312</v>
       </c>
-      <c r="R73"/>
-      <c r="S73"/>
+      <c r="R73" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S73" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8386,8 +10100,12 @@
       <c r="Q74" t="s">
         <v>312</v>
       </c>
-      <c r="R74"/>
-      <c r="S74"/>
+      <c r="R74" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S74" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8441,8 +10159,12 @@
       <c r="Q75" t="s">
         <v>312</v>
       </c>
-      <c r="R75"/>
-      <c r="S75"/>
+      <c r="R75" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S75" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8496,8 +10218,12 @@
       <c r="Q76" t="s">
         <v>312</v>
       </c>
-      <c r="R76"/>
-      <c r="S76"/>
+      <c r="R76" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S76" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8551,8 +10277,12 @@
       <c r="Q77" t="s">
         <v>312</v>
       </c>
-      <c r="R77"/>
-      <c r="S77"/>
+      <c r="R77" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S77" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8606,8 +10336,12 @@
       <c r="Q78" t="s">
         <v>312</v>
       </c>
-      <c r="R78"/>
-      <c r="S78"/>
+      <c r="R78" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S78" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8661,8 +10395,12 @@
       <c r="Q79" t="s">
         <v>312</v>
       </c>
-      <c r="R79"/>
-      <c r="S79"/>
+      <c r="R79" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S79" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8716,8 +10454,12 @@
       <c r="Q80" t="s">
         <v>312</v>
       </c>
-      <c r="R80"/>
-      <c r="S80"/>
+      <c r="R80" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S80" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8771,8 +10513,12 @@
       <c r="Q81" t="s">
         <v>312</v>
       </c>
-      <c r="R81"/>
-      <c r="S81"/>
+      <c r="R81" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S81" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8826,8 +10572,12 @@
       <c r="Q82" t="s">
         <v>312</v>
       </c>
-      <c r="R82"/>
-      <c r="S82"/>
+      <c r="R82" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S82" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8881,8 +10631,12 @@
       <c r="Q83" t="s">
         <v>312</v>
       </c>
-      <c r="R83"/>
-      <c r="S83"/>
+      <c r="R83" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S83" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8936,8 +10690,12 @@
       <c r="Q84" t="s">
         <v>312</v>
       </c>
-      <c r="R84"/>
-      <c r="S84"/>
+      <c r="R84" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S84" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8991,8 +10749,12 @@
       <c r="Q85" t="s">
         <v>312</v>
       </c>
-      <c r="R85"/>
-      <c r="S85"/>
+      <c r="R85" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S85" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9046,8 +10808,12 @@
       <c r="Q86" t="s">
         <v>312</v>
       </c>
-      <c r="R86"/>
-      <c r="S86"/>
+      <c r="R86" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S86" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9101,8 +10867,12 @@
       <c r="Q87" t="s">
         <v>312</v>
       </c>
-      <c r="R87"/>
-      <c r="S87"/>
+      <c r="R87" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S87" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9156,8 +10926,12 @@
       <c r="Q88" t="s">
         <v>312</v>
       </c>
-      <c r="R88"/>
-      <c r="S88"/>
+      <c r="R88" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S88" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9211,8 +10985,12 @@
       <c r="Q89" t="s">
         <v>312</v>
       </c>
-      <c r="R89"/>
-      <c r="S89"/>
+      <c r="R89" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S89" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9266,8 +11044,12 @@
       <c r="Q90" t="s">
         <v>312</v>
       </c>
-      <c r="R90"/>
-      <c r="S90"/>
+      <c r="R90" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S90" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9321,8 +11103,12 @@
       <c r="Q91" t="s">
         <v>312</v>
       </c>
-      <c r="R91"/>
-      <c r="S91"/>
+      <c r="R91" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S91" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9376,8 +11162,12 @@
       <c r="Q92" t="s">
         <v>312</v>
       </c>
-      <c r="R92"/>
-      <c r="S92"/>
+      <c r="R92" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S92" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
